--- a/data/OXT_All_Parameters_10162024.xlsx
+++ b/data/OXT_All_Parameters_10162024.xlsx
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W161"/>
+  <dimension ref="A1:W163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="14.42578125" customWidth="1" style="12" min="1" max="1"/>
@@ -3118,27 +3118,19 @@
       </c>
       <c r="G29" s="104" t="inlineStr">
         <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H29" s="121" t="inlineStr">
-        <is>
-          <t>1200000 ± 0.00</t>
-        </is>
-      </c>
+          <t>HEK293T cells</t>
+        </is>
+      </c>
+      <c r="H29" s="121" t="n"/>
       <c r="I29" s="112" t="inlineStr">
         <is>
           <t>4.05 ± 0.00</t>
         </is>
       </c>
-      <c r="J29" s="114" t="inlineStr">
-        <is>
-          <t>3380 ± 0.00</t>
-        </is>
-      </c>
+      <c r="J29" s="114" t="n"/>
       <c r="K29" s="167" t="inlineStr">
         <is>
-          <t>Calculated from give tau on and tau off in fig. 1c and D</t>
+          <t>k_off = 60/τ_off from receptor–Gs FRET after agonist washout (Fig. 1C–D: τ_off 14.8 ± 1.6 s A2AR, 8.4 ± 1.0 s β1AR). k_on and K_d are not curated: τ_on (49.6 / 58.1 ms) was measured at saturating 1 mM agonist and no G-protein concentration is reported, so no receptor–G protein association constant can be derived.</t>
         </is>
       </c>
       <c r="L29" s="1" t="inlineStr">
@@ -3187,27 +3179,19 @@
       </c>
       <c r="G30" s="104" t="inlineStr">
         <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H30" s="121" t="inlineStr">
-        <is>
-          <t>1030000 ± 0.00</t>
-        </is>
-      </c>
+          <t>HEK293T cells</t>
+        </is>
+      </c>
+      <c r="H30" s="121" t="n"/>
       <c r="I30" s="112" t="inlineStr">
         <is>
           <t>7.14 ± 0.00</t>
         </is>
       </c>
-      <c r="J30" s="114" t="inlineStr">
-        <is>
-          <t>6930 ± 0.00</t>
-        </is>
-      </c>
+      <c r="J30" s="114" t="n"/>
       <c r="K30" s="167" t="inlineStr">
         <is>
-          <t>Calculated from give tau on and tau off in fig. 1c and D</t>
+          <t>k_off = 60/τ_off from receptor–Gs FRET after agonist washout (Fig. 1C–D: τ_off 14.8 ± 1.6 s A2AR, 8.4 ± 1.0 s β1AR). k_on and K_d are not curated: τ_on (49.6 / 58.1 ms) was measured at saturating 1 mM agonist and no G-protein concentration is reported, so no receptor–G protein association constant can be derived.</t>
         </is>
       </c>
       <c r="L30" s="1" t="inlineStr">
@@ -6918,136 +6902,160 @@
       <c r="U87" s="34" t="n"/>
     </row>
     <row r="88" customFormat="1" s="4">
-      <c r="A88" s="43" t="n"/>
-      <c r="B88" s="42" t="n"/>
-      <c r="C88" s="110" t="n"/>
-      <c r="D88" s="1" t="n"/>
-      <c r="E88" s="1" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="1" t="n"/>
-      <c r="H88" s="49" t="n"/>
-      <c r="I88" s="163" t="n"/>
-      <c r="J88" s="161" t="n"/>
-      <c r="K88" s="33" t="n"/>
-      <c r="M88" s="35" t="n"/>
+      <c r="A88" s="51" t="inlineStr">
+        <is>
+          <t>Kact, Kinact</t>
+        </is>
+      </c>
+      <c r="B88" s="55" t="inlineStr">
+        <is>
+          <t>Gprotein activation and inactivation</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Hein et al. 2006</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>Gs</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>A2AR</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>FRET</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>HEK293T cells</t>
+        </is>
+      </c>
+      <c r="H88" s="109" t="inlineStr">
+        <is>
+          <t>121.46 ± 7.62</t>
+        </is>
+      </c>
+      <c r="I88" s="87" t="inlineStr">
+        <is>
+          <t>1.55 ± 0.064</t>
+        </is>
+      </c>
+      <c r="J88" s="160" t="n"/>
+      <c r="K88" s="65" t="inlineStr">
+        <is>
+          <t>Gs activation and deactivation, Gαs-YFP/CFP-γ2 FRET, 100 µM adenosine (τ_on at 1 mM) (Fig. 2C–D and text: τ_on 494 ± 31 ms, τ_off 38.6 ± 1.6 s, mean ± S.E.). k = 60/τ (min⁻¹); ± = 60·SE/τ² (delta method)</t>
+        </is>
+      </c>
+      <c r="L88" s="34" t="inlineStr">
+        <is>
+          <t>SR17</t>
+        </is>
+      </c>
+      <c r="M88" s="35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1074/jbc.m606713200</t>
+        </is>
+      </c>
       <c r="N88" s="33" t="n"/>
-      <c r="O88" s="33" t="n"/>
+      <c r="O88" s="47" t="n"/>
+      <c r="P88" s="33" t="n"/>
+      <c r="Q88" s="33" t="n"/>
+      <c r="R88" s="33" t="n"/>
+      <c r="S88" s="33" t="n"/>
+      <c r="T88" s="33" t="n"/>
+      <c r="U88" s="34" t="n"/>
     </row>
     <row r="89" customFormat="1" s="4">
       <c r="A89" s="51" t="inlineStr">
         <is>
-          <t>Kba</t>
-        </is>
-      </c>
-      <c r="B89" s="56" t="inlineStr">
-        <is>
-          <t>OTR:Beta arrestin binding rate</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>Busnelli et al., 2012</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Beta arrestin 1</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>OXTR</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>BRET</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>HEK293 cells</t>
-        </is>
-      </c>
-      <c r="H89" s="48" t="inlineStr">
-        <is>
-          <t>0.00708 ± 0.00208</t>
-        </is>
-      </c>
-      <c r="I89" s="163" t="n"/>
-      <c r="J89" s="162" t="n"/>
-      <c r="K89" s="33" t="n"/>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>SR7</t>
+          <t>Kact, Kinact</t>
+        </is>
+      </c>
+      <c r="B89" s="55" t="inlineStr">
+        <is>
+          <t>Gprotein activation and inactivation</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Hein et al. 2006</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Gs</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>β1AR</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>FRET</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>HEK293T cells</t>
+        </is>
+      </c>
+      <c r="H89" s="109" t="inlineStr">
+        <is>
+          <t>137.30 ± 16.97</t>
+        </is>
+      </c>
+      <c r="I89" s="87" t="inlineStr">
+        <is>
+          <t>4 ± 0.91</t>
+        </is>
+      </c>
+      <c r="J89" s="160" t="n"/>
+      <c r="K89" s="65" t="inlineStr">
+        <is>
+          <t>Gs activation and deactivation, Gαs-YFP/CFP-γ2 FRET, 100 µM norepinephrine (Fig. 2C–D and text: τ_on 437 ± 54 ms, τ_off 15.0 ± 3.4 s, mean ± S.E.). k = 60/τ (min⁻¹); ± = 60·SE/τ² (delta method)</t>
+        </is>
+      </c>
+      <c r="L89" s="34" t="inlineStr">
+        <is>
+          <t>SR17</t>
         </is>
       </c>
       <c r="M89" s="35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1074/jbc.m111.277178</t>
+          <t>https://doi.org/10.1074/jbc.m606713200</t>
         </is>
       </c>
       <c r="N89" s="33" t="n"/>
-      <c r="O89" s="33" t="n"/>
+      <c r="O89" s="47" t="n"/>
+      <c r="P89" s="33" t="n"/>
+      <c r="Q89" s="33" t="n"/>
+      <c r="R89" s="33" t="n"/>
+      <c r="S89" s="33" t="n"/>
+      <c r="T89" s="33" t="n"/>
+      <c r="U89" s="34" t="n"/>
     </row>
     <row r="90" customFormat="1" s="4">
-      <c r="A90" s="51" t="inlineStr">
-        <is>
-          <t>Kba</t>
-        </is>
-      </c>
-      <c r="B90" s="56" t="inlineStr">
-        <is>
-          <t>OTR:Beta arrestin binding rate</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Busnelli et al., 2012</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Beta arrestin 2</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>OXTR</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>BRET</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>HEK293 cells</t>
-        </is>
-      </c>
-      <c r="H90" s="136" t="inlineStr">
-        <is>
-          <t>0.0392 ± 0.00417</t>
-        </is>
-      </c>
-      <c r="I90" s="138" t="n"/>
-      <c r="J90" s="137" t="n"/>
-      <c r="K90" s="135" t="inlineStr">
-        <is>
-          <t>From fig. 6b, the given t1/2 for OT is 18 ± 2.25 sec</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>SR7</t>
-        </is>
-      </c>
-      <c r="M90" s="35" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1074/jbc.m111.277178</t>
-        </is>
-      </c>
+      <c r="A90" s="43" t="n"/>
+      <c r="B90" s="42" t="n"/>
+      <c r="C90" s="110" t="n"/>
+      <c r="D90" s="1" t="n"/>
+      <c r="E90" s="1" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="1" t="n"/>
+      <c r="H90" s="49" t="n"/>
+      <c r="I90" s="163" t="n"/>
+      <c r="J90" s="161" t="n"/>
+      <c r="K90" s="33" t="n"/>
+      <c r="M90" s="35" t="n"/>
       <c r="N90" s="33" t="n"/>
       <c r="O90" s="33" t="n"/>
     </row>
@@ -7062,47 +7070,47 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>Passoni et al., 2016</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>Beta arrestin 2</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Busnelli et al., 2012</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Beta arrestin 1</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
         <is>
           <t>OXTR</t>
         </is>
       </c>
-      <c r="F91" s="4" t="inlineStr">
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
       </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H91" s="41" t="inlineStr">
-        <is>
-          <t>0.0133 ± 0.00178</t>
-        </is>
-      </c>
-      <c r="I91" s="61" t="n"/>
-      <c r="J91" s="61" t="n"/>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>HEK293 cells</t>
+        </is>
+      </c>
+      <c r="H91" s="48" t="inlineStr">
+        <is>
+          <t>0.00708 ± 0.00208</t>
+        </is>
+      </c>
+      <c r="I91" s="163" t="n"/>
+      <c r="J91" s="162" t="n"/>
       <c r="K91" s="33" t="n"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>SR40</t>
+          <t>SR7</t>
         </is>
       </c>
       <c r="M91" s="35" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/jne.12363</t>
+          <t>https://doi.org/10.1074/jbc.m111.277178</t>
         </is>
       </c>
       <c r="N91" s="33" t="n"/>
@@ -7119,49 +7127,55 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Passoni et al., 2016</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Beta arrestin 1</t>
-        </is>
-      </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Busnelli et al., 2012</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Beta arrestin 2</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
         <is>
           <t>OXTR</t>
         </is>
       </c>
-      <c r="F92" s="4" t="inlineStr">
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
       </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H92" s="41" t="inlineStr">
-        <is>
-          <t>0.00582 ± 0.000761</t>
-        </is>
-      </c>
-      <c r="I92" s="61" t="n"/>
-      <c r="J92" s="61" t="n"/>
-      <c r="K92" s="33" t="n"/>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>HEK293 cells</t>
+        </is>
+      </c>
+      <c r="H92" s="136" t="inlineStr">
+        <is>
+          <t>0.0392 ± 0.00417</t>
+        </is>
+      </c>
+      <c r="I92" s="138" t="n"/>
+      <c r="J92" s="137" t="n"/>
+      <c r="K92" s="135" t="inlineStr">
+        <is>
+          <t>From fig. 6b, the given t1/2 for OT is 18 ± 2.25 sec</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>SR40</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1111/jne.12363</t>
-        </is>
-      </c>
+          <t>SR7</t>
+        </is>
+      </c>
+      <c r="M92" s="35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1074/jbc.m111.277178</t>
+        </is>
+      </c>
+      <c r="N92" s="33" t="n"/>
+      <c r="O92" s="33" t="n"/>
     </row>
     <row r="93" customFormat="1" s="4">
       <c r="A93" s="51" t="inlineStr">
@@ -7176,7 +7190,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Busnelli et al., 2013</t>
+          <t>Passoni et al., 2016</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -7201,7 +7215,7 @@
       </c>
       <c r="H93" s="41" t="inlineStr">
         <is>
-          <t>0.00772 ± 0.000197</t>
+          <t>0.0133 ± 0.00178</t>
         </is>
       </c>
       <c r="I93" s="61" t="n"/>
@@ -7209,14 +7223,16 @@
       <c r="K93" s="33" t="n"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>SR8</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1124/jpet.113.202994</t>
-        </is>
-      </c>
+          <t>SR40</t>
+        </is>
+      </c>
+      <c r="M93" s="35" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1111/jne.12363</t>
+        </is>
+      </c>
+      <c r="N93" s="33" t="n"/>
+      <c r="O93" s="33" t="n"/>
     </row>
     <row r="94" customFormat="1" s="4">
       <c r="A94" s="51" t="inlineStr">
@@ -7231,7 +7247,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Busnelli et al., 2013</t>
+          <t>Passoni et al., 2016</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -7254,22 +7270,22 @@
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>0.00686 ± 0.000416</t>
-        </is>
-      </c>
-      <c r="I94" s="139" t="n"/>
-      <c r="J94" s="139" t="n"/>
-      <c r="K94" s="62" t="n"/>
+      <c r="H94" s="41" t="inlineStr">
+        <is>
+          <t>0.00582 ± 0.000761</t>
+        </is>
+      </c>
+      <c r="I94" s="61" t="n"/>
+      <c r="J94" s="61" t="n"/>
+      <c r="K94" s="33" t="n"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>SR8</t>
+          <t>SR40</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1124/jpet.113.202994</t>
+          <t>https://doi.org/10.1111/jne.12363</t>
         </is>
       </c>
     </row>
@@ -7284,22 +7300,22 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Daly et al., 2023</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>Beta arrestin 1</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>V2R</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Busnelli et al., 2013</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Beta arrestin 2</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>OXTR</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
@@ -7309,26 +7325,22 @@
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H95" s="109" t="inlineStr">
-        <is>
-          <t>0.00367 ± 0.00</t>
+      <c r="H95" s="41" t="inlineStr">
+        <is>
+          <t>0.00772 ± 0.000197</t>
         </is>
       </c>
       <c r="I95" s="61" t="n"/>
-      <c r="J95" s="139" t="n"/>
-      <c r="K95" s="135" t="inlineStr">
-        <is>
-          <t>From Fig 3B t1/2 is calucated from extracted data</t>
-        </is>
-      </c>
+      <c r="J95" s="61" t="n"/>
+      <c r="K95" s="33" t="n"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>SR10</t>
+          <t>SR8</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7554/eLife.87754</t>
+          <t>https://doi.org/10.1124/jpet.113.202994</t>
         </is>
       </c>
     </row>
@@ -7343,22 +7355,22 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Daly et al., 2023</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>Beta arrestin 2</t>
-        </is>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>V2R</t>
-        </is>
-      </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Busnelli et al., 2013</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Beta arrestin 1</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>OXTR</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
@@ -7368,26 +7380,22 @@
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H96" s="109" t="inlineStr">
-        <is>
-          <t>0.00317 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I96" s="61" t="n"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>0.00686 ± 0.000416</t>
+        </is>
+      </c>
+      <c r="I96" s="139" t="n"/>
       <c r="J96" s="139" t="n"/>
-      <c r="K96" s="135" t="inlineStr">
-        <is>
-          <t>From Fig 3B t1/2 is calucated from extracted data</t>
-        </is>
-      </c>
+      <c r="K96" s="62" t="n"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>SR10</t>
+          <t>SR8</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>https://doi.org/10.7554/eLife.87754</t>
+          <t>https://doi.org/10.1124/jpet.113.202994</t>
         </is>
       </c>
     </row>
@@ -7402,22 +7410,22 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>Saulière et al., 2012</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>Beta arrestin 2</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>AT1R</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Daly et al., 2023</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Beta arrestin 1</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>V2R</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
@@ -7427,21 +7435,26 @@
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>0.0193 ± 0.00153</t>
-        </is>
-      </c>
-      <c r="I97" s="140" t="n"/>
-      <c r="J97" s="140" t="n"/>
+      <c r="H97" s="109" t="inlineStr">
+        <is>
+          <t>0.00367 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I97" s="61" t="n"/>
+      <c r="J97" s="139" t="n"/>
+      <c r="K97" s="135" t="inlineStr">
+        <is>
+          <t>From Fig 3B t1/2 is calucated from extracted data</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>SR43</t>
+          <t>SR10</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/nchembio.961</t>
+          <t>https://doi.org/10.7554/eLife.87754</t>
         </is>
       </c>
     </row>
@@ -7456,22 +7469,22 @@
           <t>OTR:Beta arrestin binding rate</t>
         </is>
       </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>Saulière et al., 2012</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Daly et al., 2023</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
         <is>
           <t>Beta arrestin 2</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>AT1R</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>V2R</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>BRET</t>
         </is>
@@ -7481,21 +7494,26 @@
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>0.00417 ± 0.000980</t>
-        </is>
-      </c>
-      <c r="I98" s="140" t="n"/>
-      <c r="J98" s="140" t="n"/>
+      <c r="H98" s="109" t="inlineStr">
+        <is>
+          <t>0.00317 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I98" s="61" t="n"/>
+      <c r="J98" s="139" t="n"/>
+      <c r="K98" s="135" t="inlineStr">
+        <is>
+          <t>From Fig 3B t1/2 is calucated from extracted data</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>SR43</t>
+          <t>SR10</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/nchembio.961</t>
+          <t>https://doi.org/10.7554/eLife.87754</t>
         </is>
       </c>
     </row>
@@ -7512,12 +7530,12 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Oakley et al., 2000</t>
+          <t>Saulière et al., 2012</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Beta arrestin 1</t>
+          <t>Beta arrestin 2</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -7537,19 +7555,19 @@
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>0.0276 ± 0.00173</t>
+          <t>0.0193 ± 0.00153</t>
         </is>
       </c>
       <c r="I99" s="140" t="n"/>
       <c r="J99" s="140" t="n"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>SR39</t>
+          <t>SR43</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1074/jbc.m910348199</t>
+          <t>https://doi.org/10.1038/nchembio.961</t>
         </is>
       </c>
     </row>
@@ -7566,7 +7584,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Oakley et al., 2000</t>
+          <t>Saulière et al., 2012</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -7591,23 +7609,21 @@
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>0.0261 ± 0.00126</t>
+          <t>0.00417 ± 0.000980</t>
         </is>
       </c>
       <c r="I100" s="140" t="n"/>
       <c r="J100" s="140" t="n"/>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>SR39</t>
-        </is>
-      </c>
-      <c r="M100" s="4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1074/jbc.m910348199</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="n"/>
-      <c r="O100" s="4" t="n"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SR43</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1038/nchembio.961</t>
+        </is>
+      </c>
     </row>
     <row r="101" customFormat="1" s="4">
       <c r="A101" s="51" t="inlineStr">
@@ -7632,7 +7648,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>β2AR</t>
+          <t>AT1R</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -7647,9 +7663,11 @@
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>0.0194 ± 0.0010</t>
-        </is>
-      </c>
+          <t>0.0276 ± 0.00173</t>
+        </is>
+      </c>
+      <c r="I101" s="140" t="n"/>
+      <c r="J101" s="140" t="n"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>SR39</t>
@@ -7684,7 +7702,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>β2AR</t>
+          <t>AT1R</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -7699,19 +7717,23 @@
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>0.0361 ± 0.00195</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
+          <t>0.0261 ± 0.00126</t>
+        </is>
+      </c>
+      <c r="I102" s="140" t="n"/>
+      <c r="J102" s="140" t="n"/>
+      <c r="L102" s="4" t="inlineStr">
         <is>
           <t>SR39</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr">
+      <c r="M102" s="4" t="inlineStr">
         <is>
           <t>https://doi.org/10.1074/jbc.m910348199</t>
         </is>
       </c>
+      <c r="N102" s="4" t="n"/>
+      <c r="O102" s="4" t="n"/>
     </row>
     <row r="103" customFormat="1" s="4">
       <c r="A103" s="51" t="inlineStr">
@@ -7726,12 +7748,12 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Krasel et al., 2005</t>
-        </is>
-      </c>
-      <c r="D103" s="63" t="inlineStr">
-        <is>
-          <t>Beta arrestin 2</t>
+          <t>Oakley et al., 2000</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Beta arrestin 1</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
@@ -7741,7 +7763,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>FRET</t>
+          <t>BRET</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -7751,17 +7773,17 @@
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>0.035 ± 0.01</t>
+          <t>0.0194 ± 0.0010</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>SR23</t>
+          <t>SR39</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1074/jbc.m413078200</t>
+          <t>https://doi.org/10.1074/jbc.m910348199</t>
         </is>
       </c>
     </row>
@@ -7778,12 +7800,12 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Luttrell et al., 1999</t>
-        </is>
-      </c>
-      <c r="D104" s="63" t="inlineStr">
-        <is>
-          <t>Beta arrestin 1</t>
+          <t>Oakley et al., 2000</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Beta arrestin 2</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -7793,149 +7815,142 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Western Blot</t>
+          <t>BRET</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>HEK293 cells</t>
+          <t>HEK293 Cells</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>0.00774 ± 0.00</t>
+          <t>0.0361 ± 0.00195</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>SR30</t>
+          <t>SR39</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1126/science.283.5402.655</t>
+          <t>https://doi.org/10.1074/jbc.m910348199</t>
         </is>
       </c>
     </row>
     <row r="105" customFormat="1" s="4">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="68" t="n"/>
-      <c r="E105" s="44" t="n"/>
-      <c r="F105" s="1" t="n"/>
-      <c r="G105" s="1" t="n"/>
-      <c r="H105" s="9" t="n"/>
+      <c r="A105" s="51" t="inlineStr">
+        <is>
+          <t>Kba</t>
+        </is>
+      </c>
+      <c r="B105" s="56" t="inlineStr">
+        <is>
+          <t>OTR:Beta arrestin binding rate</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Krasel et al., 2005</t>
+        </is>
+      </c>
+      <c r="D105" s="63" t="inlineStr">
+        <is>
+          <t>Beta arrestin 2</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>β2AR</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>FRET</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>0.035 ± 0.01</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>SR23</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1074/jbc.m413078200</t>
+        </is>
+      </c>
     </row>
     <row r="106" customFormat="1" s="4">
       <c r="A106" s="51" t="inlineStr">
         <is>
-          <t>Kint</t>
-        </is>
-      </c>
-      <c r="B106" s="53" t="inlineStr">
-        <is>
-          <t>Phosphorylated OTR internalization</t>
-        </is>
-      </c>
-      <c r="C106" s="29" t="inlineStr">
-        <is>
-          <t>Smith, et al., 2006</t>
-        </is>
-      </c>
-      <c r="E106" s="7" t="inlineStr">
-        <is>
-          <t>OXTR</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="inlineStr">
-        <is>
-          <t>ELISA, HA-OTR</t>
-        </is>
-      </c>
-      <c r="G106" s="3" t="inlineStr">
+          <t>Kba</t>
+        </is>
+      </c>
+      <c r="B106" s="56" t="inlineStr">
+        <is>
+          <t>OTR:Beta arrestin binding rate</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Luttrell et al., 1999</t>
+        </is>
+      </c>
+      <c r="D106" s="63" t="inlineStr">
+        <is>
+          <t>Beta arrestin 1</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>β2AR</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Western Blot</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>HEK293 cells</t>
         </is>
       </c>
-      <c r="H106" s="11" t="inlineStr">
-        <is>
-          <t>0.31 ± 0.15</t>
-        </is>
-      </c>
-      <c r="K106" s="141" t="inlineStr">
-        <is>
-          <t>Calculated from t1/2 = 2.3 given on Page 381 First Para</t>
-        </is>
-      </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>SR46</t>
-        </is>
-      </c>
-      <c r="M106" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1210/me.2005-0031</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="n"/>
-      <c r="O106" s="3" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>0.00774 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>SR30</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1126/science.283.5402.655</t>
+        </is>
+      </c>
     </row>
     <row r="107" customFormat="1" s="4">
-      <c r="A107" s="51" t="inlineStr">
-        <is>
-          <t>Kint</t>
-        </is>
-      </c>
-      <c r="B107" s="53" t="inlineStr">
-        <is>
-          <t>Phosphorylated OTR internalization</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>Conti, et al., 2009</t>
-        </is>
-      </c>
-      <c r="D107" s="86" t="n"/>
-      <c r="E107" s="7" t="inlineStr">
-        <is>
-          <t>OXTR</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="inlineStr">
-        <is>
-          <t>Immunofluorescence imaging</t>
-        </is>
-      </c>
-      <c r="G107" s="3" t="inlineStr">
-        <is>
-          <t>htert human myometrial cells</t>
-        </is>
-      </c>
-      <c r="H107" s="136" t="inlineStr">
-        <is>
-          <t>0.046 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I107" s="141" t="n"/>
-      <c r="J107" s="141" t="n"/>
-      <c r="K107" s="150" t="inlineStr">
-        <is>
-          <t>Calculated from the t1/2 = 2.36 given on page E537 in OTR Recycling in Myometrial Cells subheading</t>
-        </is>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>SR9</t>
-        </is>
-      </c>
-      <c r="M107" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpendo.90590.2008</t>
-        </is>
-      </c>
-      <c r="N107" s="3" t="n"/>
-      <c r="O107" s="3" t="n"/>
+      <c r="A107" s="6" t="n"/>
+      <c r="B107" s="6" t="n"/>
+      <c r="C107" s="68" t="n"/>
+      <c r="E107" s="44" t="n"/>
+      <c r="F107" s="1" t="n"/>
+      <c r="G107" s="1" t="n"/>
+      <c r="H107" s="9" t="n"/>
     </row>
     <row r="108" customFormat="1" s="4">
       <c r="A108" s="51" t="inlineStr">
@@ -7948,41 +7963,48 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C108" s="69" t="inlineStr">
-        <is>
-          <t>Gulappa et al., 2011</t>
-        </is>
-      </c>
-      <c r="E108" s="77" t="inlineStr">
-        <is>
-          <t>LHR</t>
-        </is>
-      </c>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>Western Blot</t>
-        </is>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>HEK293 cells tansfected with LHR</t>
-        </is>
-      </c>
-      <c r="H108" s="28" t="inlineStr">
-        <is>
-          <t>0.0297 ± 0.0013</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>SR15</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s00018-010-0594-1</t>
-        </is>
-      </c>
+      <c r="C108" s="29" t="inlineStr">
+        <is>
+          <t>Smith, et al., 2006</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>OXTR</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>ELISA, HA-OTR</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>HEK293 cells</t>
+        </is>
+      </c>
+      <c r="H108" s="11" t="inlineStr">
+        <is>
+          <t>0.31 ± 0.15</t>
+        </is>
+      </c>
+      <c r="K108" s="141" t="inlineStr">
+        <is>
+          <t>Calculated from t1/2 = 2.3 given on Page 381 First Para</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>SR46</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1210/me.2005-0031</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="n"/>
+      <c r="O108" s="3" t="n"/>
     </row>
     <row r="109" customFormat="1" s="4">
       <c r="A109" s="51" t="inlineStr">
@@ -7995,41 +8017,51 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C109" s="70" t="inlineStr">
-        <is>
-          <t>Berrada et al., 2000</t>
-        </is>
-      </c>
-      <c r="E109" s="98" t="inlineStr">
-        <is>
-          <t>V1R</t>
-        </is>
-      </c>
-      <c r="F109" s="4" t="inlineStr">
-        <is>
-          <t>Western Blot</t>
-        </is>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>CHO cells</t>
-        </is>
-      </c>
-      <c r="H109" s="28" t="inlineStr">
-        <is>
-          <t>0.154 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>SR2</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1074/jbc.m002288200</t>
-        </is>
-      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Conti, et al., 2009</t>
+        </is>
+      </c>
+      <c r="D109" s="86" t="n"/>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>OXTR</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Immunofluorescence imaging</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>htert human myometrial cells</t>
+        </is>
+      </c>
+      <c r="H109" s="136" t="inlineStr">
+        <is>
+          <t>0.046 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I109" s="141" t="n"/>
+      <c r="J109" s="141" t="n"/>
+      <c r="K109" s="150" t="inlineStr">
+        <is>
+          <t>Calculated from the t1/2 = 2.36 given on page E537 in OTR Recycling in Myometrial Cells subheading</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>SR9</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1152/ajpendo.90590.2008</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="n"/>
+      <c r="O109" s="3" t="n"/>
     </row>
     <row r="110" customFormat="1" s="4">
       <c r="A110" s="51" t="inlineStr">
@@ -8042,45 +8074,39 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C110" s="70" t="inlineStr">
-        <is>
-          <t>Pfeiffer et al., 1998</t>
-        </is>
-      </c>
-      <c r="D110" s="84" t="n"/>
-      <c r="E110" s="99" t="inlineStr">
-        <is>
-          <t>V2R</t>
+      <c r="C110" s="69" t="inlineStr">
+        <is>
+          <t>Gulappa et al., 2011</t>
+        </is>
+      </c>
+      <c r="E110" s="77" t="inlineStr">
+        <is>
+          <t>LHR</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Immunofluorescence microscopy</t>
+          <t>Western Blot</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>HEK293 Cells</t>
+          <t>HEK293 cells tansfected with LHR</t>
         </is>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
-          <t>0.1095 ± 0.0105</t>
-        </is>
-      </c>
-      <c r="K110" s="141" t="inlineStr">
-        <is>
-          <t>Abstract and figure 4</t>
+          <t>0.0297 ± 0.0013</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>SR42</t>
+          <t>SR15</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1006/excr.1998.4159</t>
+          <t>https://doi.org/10.1007/s00018-010-0594-1</t>
         </is>
       </c>
     </row>
@@ -8097,18 +8123,17 @@
       </c>
       <c r="C111" s="70" t="inlineStr">
         <is>
-          <t>Thibonnier et al., 2001</t>
-        </is>
-      </c>
-      <c r="D111" s="84" t="n"/>
-      <c r="E111" s="99" t="inlineStr">
+          <t>Berrada et al., 2000</t>
+        </is>
+      </c>
+      <c r="E111" s="98" t="inlineStr">
         <is>
           <t>V1R</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Radioligand binding assays</t>
+          <t>Western Blot</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -8118,17 +8143,17 @@
       </c>
       <c r="H111" s="28" t="inlineStr">
         <is>
-          <t>0.14 ± 0.00</t>
+          <t>0.154 ± 0.00</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>SR49</t>
+          <t>SR2</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
+          <t>https://doi.org/10.1074/jbc.m002288200</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8170,7 @@
       </c>
       <c r="C112" s="70" t="inlineStr">
         <is>
-          <t>Thibonnier et al., 2001</t>
+          <t>Pfeiffer et al., 1998</t>
         </is>
       </c>
       <c r="D112" s="84" t="n"/>
@@ -8156,27 +8181,32 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Radioligand binding assays</t>
+          <t>Immunofluorescence microscopy</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>CHO cells</t>
+          <t>HEK293 Cells</t>
         </is>
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
-          <t>0.053 ± 0.00</t>
+          <t>0.1095 ± 0.0105</t>
+        </is>
+      </c>
+      <c r="K112" s="141" t="inlineStr">
+        <is>
+          <t>Abstract and figure 4</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>SR49</t>
+          <t>SR42</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
+          <t>https://doi.org/10.1006/excr.1998.4159</t>
         </is>
       </c>
     </row>
@@ -8191,42 +8221,40 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C113" s="147" t="inlineStr">
-        <is>
-          <t>Levoye et al., 2015</t>
-        </is>
-      </c>
-      <c r="D113" s="148" t="n"/>
-      <c r="E113" s="147" t="inlineStr">
-        <is>
-          <t>CXCR7</t>
-        </is>
-      </c>
-      <c r="F113" s="110" t="inlineStr">
-        <is>
-          <t>DERET</t>
-        </is>
-      </c>
-      <c r="G113" s="149" t="inlineStr">
-        <is>
-          <t>HEK-293 cells</t>
+      <c r="C113" s="70" t="inlineStr">
+        <is>
+          <t>Thibonnier et al., 2001</t>
+        </is>
+      </c>
+      <c r="D113" s="84" t="n"/>
+      <c r="E113" s="99" t="inlineStr">
+        <is>
+          <t>V1R</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Radioligand binding assays</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
         </is>
       </c>
       <c r="H113" s="28" t="inlineStr">
         <is>
-          <t>0.046742128 ± 0.01927189</t>
-        </is>
-      </c>
-      <c r="I113" s="145" t="n"/>
-      <c r="J113" s="141" t="n"/>
+          <t>0.14 ± 0.00</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>SR26</t>
+          <t>SR49</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fendo.2015.00167</t>
+          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
         </is>
       </c>
     </row>
@@ -8241,42 +8269,40 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C114" s="142" t="inlineStr">
-        <is>
-          <t>Levoye et al., 2015</t>
-        </is>
-      </c>
-      <c r="D114" s="143" t="n"/>
-      <c r="E114" s="142" t="inlineStr">
-        <is>
-          <t>CXCR4</t>
-        </is>
-      </c>
-      <c r="F114" s="144" t="inlineStr">
-        <is>
-          <t>DERET</t>
-        </is>
-      </c>
-      <c r="G114" s="146" t="inlineStr">
-        <is>
-          <t>HEK-293 cells</t>
+      <c r="C114" s="70" t="inlineStr">
+        <is>
+          <t>Thibonnier et al., 2001</t>
+        </is>
+      </c>
+      <c r="D114" s="84" t="n"/>
+      <c r="E114" s="99" t="inlineStr">
+        <is>
+          <t>V2R</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Radioligand binding assays</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
         </is>
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
-          <t>0.03299299 ± 0.01059972</t>
-        </is>
-      </c>
-      <c r="I114" s="145" t="n"/>
-      <c r="J114" s="141" t="n"/>
+          <t>0.053 ± 0.00</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>SR26</t>
+          <t>SR49</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3389/fendo.2015.00167</t>
+          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
         </is>
       </c>
     </row>
@@ -8291,30 +8317,30 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C115" s="142" t="inlineStr">
+      <c r="C115" s="147" t="inlineStr">
         <is>
           <t>Levoye et al., 2015</t>
         </is>
       </c>
-      <c r="D115" s="143" t="n"/>
-      <c r="E115" s="142" t="inlineStr">
-        <is>
-          <t>V1AR</t>
-        </is>
-      </c>
-      <c r="F115" s="144" t="inlineStr">
+      <c r="D115" s="148" t="n"/>
+      <c r="E115" s="147" t="inlineStr">
+        <is>
+          <t>CXCR7</t>
+        </is>
+      </c>
+      <c r="F115" s="110" t="inlineStr">
         <is>
           <t>DERET</t>
         </is>
       </c>
-      <c r="G115" s="146" t="inlineStr">
+      <c r="G115" s="149" t="inlineStr">
         <is>
           <t>HEK-293 cells</t>
         </is>
       </c>
       <c r="H115" s="28" t="inlineStr">
         <is>
-          <t>0.064853081 ± 0.00</t>
+          <t>0.046742128 ± 0.01927189</t>
         </is>
       </c>
       <c r="I115" s="145" t="n"/>
@@ -8341,46 +8367,42 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C116" s="72" t="inlineStr">
-        <is>
-          <t>Bulseco et al., 1996</t>
-        </is>
-      </c>
-      <c r="E116" s="78" t="inlineStr">
-        <is>
-          <t>M2R</t>
-        </is>
-      </c>
-      <c r="F116" s="34" t="inlineStr">
-        <is>
-          <t>Radiolabelling</t>
-        </is>
-      </c>
-      <c r="G116" s="35" t="inlineStr">
-        <is>
-          <t>CHO cells</t>
+      <c r="C116" s="142" t="inlineStr">
+        <is>
+          <t>Levoye et al., 2015</t>
+        </is>
+      </c>
+      <c r="D116" s="143" t="n"/>
+      <c r="E116" s="142" t="inlineStr">
+        <is>
+          <t>CXCR4</t>
+        </is>
+      </c>
+      <c r="F116" s="144" t="inlineStr">
+        <is>
+          <t>DERET</t>
+        </is>
+      </c>
+      <c r="G116" s="146" t="inlineStr">
+        <is>
+          <t>HEK-293 cells</t>
         </is>
       </c>
       <c r="H116" s="28" t="inlineStr">
         <is>
-          <t>0.021275 ± 0.009725</t>
-        </is>
-      </c>
-      <c r="I116" s="65" t="n"/>
-      <c r="J116" s="65" t="n"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Protease-activated receptor-1 (PAR1), a G protein–coupled receptor</t>
-        </is>
-      </c>
+          <t>0.03299299 ± 0.01059972</t>
+        </is>
+      </c>
+      <c r="I116" s="145" t="n"/>
+      <c r="J116" s="141" t="n"/>
       <c r="L116" t="inlineStr">
         <is>
-          <t>SR5</t>
+          <t>SR26</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+          <t>https://doi.org/10.3389/fendo.2015.00167</t>
         </is>
       </c>
     </row>
@@ -8395,151 +8417,161 @@
           <t>Phosphorylated OTR internalization</t>
         </is>
       </c>
-      <c r="C117" s="72" t="inlineStr">
-        <is>
-          <t>Mandić et al., 2014</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>β2AR</t>
-        </is>
-      </c>
-      <c r="F117" s="34" t="inlineStr">
-        <is>
-          <t>ELISA</t>
-        </is>
-      </c>
-      <c r="G117" s="35" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
+      <c r="C117" s="142" t="inlineStr">
+        <is>
+          <t>Levoye et al., 2015</t>
+        </is>
+      </c>
+      <c r="D117" s="143" t="n"/>
+      <c r="E117" s="142" t="inlineStr">
+        <is>
+          <t>V1AR</t>
+        </is>
+      </c>
+      <c r="F117" s="144" t="inlineStr">
+        <is>
+          <t>DERET</t>
+        </is>
+      </c>
+      <c r="G117" s="146" t="inlineStr">
+        <is>
+          <t>HEK-293 cells</t>
         </is>
       </c>
       <c r="H117" s="28" t="inlineStr">
         <is>
-          <t>0.08 ± 0.01</t>
-        </is>
-      </c>
-      <c r="I117" s="65" t="n"/>
-      <c r="J117" s="65" t="n"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>t1/2 = 8.6 ± 1.3 min (β2AR alone, isoproterenol; Results); k = ln2/t1/2</t>
-        </is>
-      </c>
+          <t>0.064853081 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I117" s="145" t="n"/>
+      <c r="J117" s="141" t="n"/>
       <c r="L117" t="inlineStr">
         <is>
-          <t>SR31</t>
+          <t>SR26</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pone.0112664</t>
+          <t>https://doi.org/10.3389/fendo.2015.00167</t>
         </is>
       </c>
     </row>
     <row r="118" ht="15" customFormat="1" customHeight="1" s="4">
-      <c r="A118" s="6" t="n"/>
-      <c r="B118" s="43" t="n"/>
-      <c r="C118" s="73" t="n"/>
-      <c r="E118" s="79" t="n"/>
-      <c r="F118" s="44" t="n"/>
-      <c r="G118" s="36" t="n"/>
-      <c r="H118" s="39" t="n"/>
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>Kint</t>
+        </is>
+      </c>
+      <c r="B118" s="53" t="inlineStr">
+        <is>
+          <t>Phosphorylated OTR internalization</t>
+        </is>
+      </c>
+      <c r="C118" s="72" t="inlineStr">
+        <is>
+          <t>Bulseco et al., 1996</t>
+        </is>
+      </c>
+      <c r="E118" s="78" t="inlineStr">
+        <is>
+          <t>M2R</t>
+        </is>
+      </c>
+      <c r="F118" s="34" t="inlineStr">
+        <is>
+          <t>Radiolabelling</t>
+        </is>
+      </c>
+      <c r="G118" s="35" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
+        </is>
+      </c>
+      <c r="H118" s="28" t="inlineStr">
+        <is>
+          <t>0.021275 ± 0.009725</t>
+        </is>
+      </c>
+      <c r="I118" s="65" t="n"/>
+      <c r="J118" s="65" t="n"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Protease-activated receptor-1 (PAR1), a G protein–coupled receptor</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>SR5</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+        </is>
+      </c>
     </row>
     <row r="119" customFormat="1" s="4">
       <c r="A119" s="51" t="inlineStr">
         <is>
-          <t>Kcons_int</t>
+          <t>Kint</t>
         </is>
       </c>
       <c r="B119" s="53" t="inlineStr">
         <is>
-          <t>Constitutive OTR internalization</t>
-        </is>
-      </c>
-      <c r="C119" s="74" t="inlineStr">
-        <is>
-          <t>Marco Scarselli, et al., 2009</t>
-        </is>
-      </c>
-      <c r="E119" s="80" t="inlineStr">
-        <is>
-          <t>M3R</t>
-        </is>
-      </c>
-      <c r="F119" s="30" t="inlineStr">
-        <is>
-          <t>Immunofluorescence imaging, HA-OTR</t>
-        </is>
-      </c>
-      <c r="G119" s="3" t="inlineStr">
-        <is>
-          <t>HeLa Cells</t>
-        </is>
-      </c>
-      <c r="H119" s="37" t="inlineStr">
-        <is>
-          <t>0.0105 ± 0.0025</t>
+          <t>Phosphorylated OTR internalization</t>
+        </is>
+      </c>
+      <c r="C119" s="72" t="inlineStr">
+        <is>
+          <t>Mandić et al., 2014</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>β2AR</t>
+        </is>
+      </c>
+      <c r="F119" s="34" t="inlineStr">
+        <is>
+          <t>ELISA</t>
+        </is>
+      </c>
+      <c r="G119" s="35" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
+        </is>
+      </c>
+      <c r="H119" s="28" t="inlineStr">
+        <is>
+          <t>0.08 ± 0.01</t>
+        </is>
+      </c>
+      <c r="I119" s="65" t="n"/>
+      <c r="J119" s="65" t="n"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>t1/2 = 8.6 ± 1.3 min (β2AR alone, isoproterenol; Results); k = ln2/t1/2</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>SR44</t>
+          <t>SR31</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1074/jbc.m806819200</t>
+          <t>https://doi.org/10.1371/journal.pone.0112664</t>
         </is>
       </c>
     </row>
     <row r="120" customFormat="1" s="4">
-      <c r="A120" s="51" t="inlineStr">
-        <is>
-          <t>Kcons_int</t>
-        </is>
-      </c>
-      <c r="B120" s="53" t="inlineStr">
-        <is>
-          <t>Constitutive OTR internalization</t>
-        </is>
-      </c>
-      <c r="C120" s="72" t="inlineStr">
-        <is>
-          <t>Levoye et al., 2015</t>
-        </is>
-      </c>
-      <c r="E120" s="78" t="inlineStr">
-        <is>
-          <t>CXCR7</t>
-        </is>
-      </c>
-      <c r="F120" s="34" t="inlineStr">
-        <is>
-          <t>DERET</t>
-        </is>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>CHO or HEK-293 cells</t>
-        </is>
-      </c>
-      <c r="H120" s="8" t="inlineStr">
-        <is>
-          <t>0.04621 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>SR26</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3389/fendo.2015.00167</t>
-        </is>
-      </c>
+      <c r="A120" s="6" t="n"/>
+      <c r="B120" s="43" t="n"/>
+      <c r="C120" s="73" t="n"/>
+      <c r="E120" s="79" t="n"/>
+      <c r="F120" s="44" t="n"/>
+      <c r="G120" s="36" t="n"/>
+      <c r="H120" s="39" t="n"/>
     </row>
     <row r="121" customFormat="1" s="4">
       <c r="A121" s="51" t="inlineStr">
@@ -8552,39 +8584,39 @@
           <t>Constitutive OTR internalization</t>
         </is>
       </c>
-      <c r="C121" s="75" t="inlineStr">
-        <is>
-          <t>Bulseco et al., 1996</t>
-        </is>
-      </c>
-      <c r="E121" s="81" t="inlineStr">
-        <is>
-          <t>M2R</t>
-        </is>
-      </c>
-      <c r="F121" s="4" t="inlineStr">
-        <is>
-          <t>Radiolabelling</t>
-        </is>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>CHO cells</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>0.00525 ± 0.00305</t>
+      <c r="C121" s="74" t="inlineStr">
+        <is>
+          <t>Marco Scarselli, et al., 2009</t>
+        </is>
+      </c>
+      <c r="E121" s="80" t="inlineStr">
+        <is>
+          <t>M3R</t>
+        </is>
+      </c>
+      <c r="F121" s="30" t="inlineStr">
+        <is>
+          <t>Immunofluorescence imaging, HA-OTR</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>HeLa Cells</t>
+        </is>
+      </c>
+      <c r="H121" s="37" t="inlineStr">
+        <is>
+          <t>0.0105 ± 0.0025</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>SR5</t>
+          <t>SR44</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+          <t>https://doi.org/10.1074/jbc.m806819200</t>
         </is>
       </c>
     </row>
@@ -8599,39 +8631,39 @@
           <t>Constitutive OTR internalization</t>
         </is>
       </c>
-      <c r="C122" s="35" t="inlineStr">
-        <is>
-          <t>Wolfe et al., 2007</t>
-        </is>
-      </c>
-      <c r="E122" s="34" t="inlineStr">
-        <is>
-          <t>PAR1</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>ELISA</t>
+      <c r="C122" s="72" t="inlineStr">
+        <is>
+          <t>Levoye et al., 2015</t>
+        </is>
+      </c>
+      <c r="E122" s="78" t="inlineStr">
+        <is>
+          <t>CXCR7</t>
+        </is>
+      </c>
+      <c r="F122" s="34" t="inlineStr">
+        <is>
+          <t>DERET</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>HeLa Cells</t>
-        </is>
-      </c>
-      <c r="H122" s="40" t="inlineStr">
-        <is>
-          <t>0.0462 ± 0.00</t>
+          <t>CHO or HEK-293 cells</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>0.04621 ± 0.00</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>SR55</t>
+          <t>SR26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1083/jcb.200610154</t>
+          <t>https://doi.org/10.3389/fendo.2015.00167</t>
         </is>
       </c>
     </row>
@@ -8646,39 +8678,39 @@
           <t>Constitutive OTR internalization</t>
         </is>
       </c>
-      <c r="C123" s="35" t="inlineStr">
-        <is>
-          <t>Liebick et al., 2016</t>
-        </is>
-      </c>
-      <c r="E123" s="34" t="inlineStr">
-        <is>
-          <t>CXCR4</t>
+      <c r="C123" s="75" t="inlineStr">
+        <is>
+          <t>Bulseco et al., 1996</t>
+        </is>
+      </c>
+      <c r="E123" s="81" t="inlineStr">
+        <is>
+          <t>M2R</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Flow cytometry</t>
+          <t>Radiolabelling</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>Rat basophilic leukemia cells clone 2H3 (RBL 2H3)</t>
+          <t>CHO cells</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>0.00275 ± 0.00025</t>
+          <t>0.00525 ± 0.00305</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>SR29</t>
+          <t>SR5</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pone.0157502</t>
+          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
         </is>
       </c>
     </row>
@@ -8693,154 +8725,148 @@
           <t>Constitutive OTR internalization</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C124" s="35" t="inlineStr">
+        <is>
+          <t>Wolfe et al., 2007</t>
+        </is>
+      </c>
+      <c r="E124" s="34" t="inlineStr">
+        <is>
+          <t>PAR1</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>ELISA</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>HeLa Cells</t>
+        </is>
+      </c>
+      <c r="H124" s="40" t="inlineStr">
+        <is>
+          <t>0.0462 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>SR55</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1083/jcb.200610154</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>Kcons_int</t>
+        </is>
+      </c>
+      <c r="B125" s="53" t="inlineStr">
+        <is>
+          <t>Constitutive OTR internalization</t>
+        </is>
+      </c>
+      <c r="C125" s="35" t="inlineStr">
         <is>
           <t>Liebick et al., 2016</t>
         </is>
       </c>
-      <c r="D124" s="86" t="n"/>
-      <c r="E124" s="5" t="inlineStr">
-        <is>
-          <t>CXCR5</t>
-        </is>
-      </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="E125" s="34" t="inlineStr">
+        <is>
+          <t>CXCR4</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
         <is>
           <t>Flow cytometry</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G125" s="4" t="inlineStr">
         <is>
           <t>Rat basophilic leukemia cells clone 2H3 (RBL 2H3)</t>
         </is>
       </c>
-      <c r="H124" s="87" t="inlineStr">
-        <is>
-          <t>0.00315 ± 0.00015</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>0.00275 ± 0.00025</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
         <is>
           <t>SR29</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>https://doi.org/10.1371/journal.pone.0157502</t>
         </is>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="n"/>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="68" t="n"/>
-      <c r="D125" s="4" t="n"/>
-      <c r="E125" s="44" t="n"/>
-      <c r="F125" s="1" t="n"/>
-      <c r="G125" s="1" t="n"/>
-      <c r="H125" s="9" t="n"/>
-      <c r="L125" s="4" t="n"/>
-      <c r="M125" s="4" t="n"/>
-      <c r="N125" s="4" t="n"/>
-      <c r="O125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="51" t="inlineStr">
         <is>
-          <t>Krec</t>
+          <t>Kcons_int</t>
         </is>
       </c>
       <c r="B126" s="53" t="inlineStr">
         <is>
-          <t>OXTR recycling rate (back to surface)</t>
-        </is>
-      </c>
-      <c r="C126" s="29" t="inlineStr">
-        <is>
-          <t>Conti, et al., 2009</t>
-        </is>
-      </c>
-      <c r="D126" s="4" t="n"/>
-      <c r="E126" s="30" t="inlineStr">
-        <is>
-          <t>OXTR</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>Immunofluorescence imaging</t>
-        </is>
-      </c>
-      <c r="G126" s="3" t="inlineStr">
-        <is>
-          <t>hTERT human myometrial cells</t>
-        </is>
-      </c>
-      <c r="H126" s="11" t="inlineStr">
-        <is>
-          <t>0.0575 ± 0.0115</t>
-        </is>
-      </c>
-      <c r="L126" s="4" t="inlineStr">
-        <is>
-          <t>SR9</t>
-        </is>
-      </c>
-      <c r="M126" s="4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1152/ajpendo.90590.2008</t>
-        </is>
-      </c>
-      <c r="N126" s="4" t="n"/>
-      <c r="O126" s="4" t="n"/>
+          <t>Constitutive OTR internalization</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Liebick et al., 2016</t>
+        </is>
+      </c>
+      <c r="D126" s="86" t="n"/>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>CXCR5</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Flow cytometry</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Rat basophilic leukemia cells clone 2H3 (RBL 2H3)</t>
+        </is>
+      </c>
+      <c r="H126" s="87" t="inlineStr">
+        <is>
+          <t>0.00315 ± 0.00015</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>SR29</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1371/journal.pone.0157502</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="51" t="inlineStr">
-        <is>
-          <t>Krec</t>
-        </is>
-      </c>
-      <c r="B127" s="53" t="inlineStr">
-        <is>
-          <t>OXTR recycling rate (back to surface)</t>
-        </is>
-      </c>
-      <c r="C127" s="35" t="inlineStr">
-        <is>
-          <t>Nisar, et al., 2010</t>
-        </is>
-      </c>
+      <c r="A127" s="6" t="n"/>
+      <c r="B127" s="6" t="n"/>
+      <c r="C127" s="68" t="n"/>
       <c r="D127" s="4" t="n"/>
-      <c r="E127" s="34" t="inlineStr">
-        <is>
-          <t>P2Y12R</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>ELISA</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>human astrocytoma cells</t>
-        </is>
-      </c>
-      <c r="H127" s="8" t="inlineStr">
-        <is>
-          <t>0.031 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>SR38</t>
-        </is>
-      </c>
-      <c r="M127" s="4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1111/j.1600-0854.2010.01035.x</t>
-        </is>
-      </c>
+      <c r="E127" s="44" t="n"/>
+      <c r="F127" s="1" t="n"/>
+      <c r="G127" s="1" t="n"/>
+      <c r="H127" s="9" t="n"/>
+      <c r="L127" s="4" t="n"/>
+      <c r="M127" s="4" t="n"/>
       <c r="N127" s="4" t="n"/>
       <c r="O127" s="4" t="n"/>
     </row>
@@ -8855,40 +8881,40 @@
           <t>OXTR recycling rate (back to surface)</t>
         </is>
       </c>
-      <c r="C128" s="35" t="inlineStr">
-        <is>
-          <t>Nisar, et al., 2010</t>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>Conti, et al., 2009</t>
         </is>
       </c>
       <c r="D128" s="4" t="n"/>
-      <c r="E128" s="34" t="inlineStr">
-        <is>
-          <t>P2Y1R</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>ELISA</t>
-        </is>
-      </c>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t>human astrocytoma cells</t>
-        </is>
-      </c>
-      <c r="H128" s="8" t="inlineStr">
-        <is>
-          <t>0.0031 ± 0.00</t>
+      <c r="E128" s="30" t="inlineStr">
+        <is>
+          <t>OXTR</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>Immunofluorescence imaging</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>hTERT human myometrial cells</t>
+        </is>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>0.0575 ± 0.0115</t>
         </is>
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>SR38</t>
+          <t>SR9</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1600-0854.2010.01035.x</t>
+          <t>https://doi.org/10.1152/ajpendo.90590.2008</t>
         </is>
       </c>
       <c r="N128" s="4" t="n"/>
@@ -8907,38 +8933,38 @@
       </c>
       <c r="C129" s="35" t="inlineStr">
         <is>
-          <t>Gulappa et al., 2011</t>
+          <t>Nisar, et al., 2010</t>
         </is>
       </c>
       <c r="D129" s="4" t="n"/>
-      <c r="E129" s="82" t="inlineStr">
-        <is>
-          <t>LHR</t>
+      <c r="E129" s="34" t="inlineStr">
+        <is>
+          <t>P2Y12R</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Western Blot</t>
+          <t>ELISA</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>HEK293 Cells</t>
+          <t>human astrocytoma cells</t>
         </is>
       </c>
       <c r="H129" s="8" t="inlineStr">
         <is>
-          <t>0.0033 ± 0.0003</t>
+          <t>0.031 ± 0.00</t>
         </is>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>SR15</t>
+          <t>SR38</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s00018-010-0594-1</t>
+          <t>https://doi.org/10.1111/j.1600-0854.2010.01035.x</t>
         </is>
       </c>
       <c r="N129" s="4" t="n"/>
@@ -8957,38 +8983,38 @@
       </c>
       <c r="C130" s="35" t="inlineStr">
         <is>
-          <t>Ghosh, et al., 1994</t>
+          <t>Nisar, et al., 2010</t>
         </is>
       </c>
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="34" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>P2Y1R</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Radiolabelling</t>
+          <t>ELISA</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>CHO cells</t>
+          <t>human astrocytoma cells</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>0.09902 ± 0.00</t>
+          <t>0.0031 ± 0.00</t>
         </is>
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>SR14</t>
+          <t>SR38</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1242/jcs.107.8.2177</t>
+          <t>https://doi.org/10.1111/j.1600-0854.2010.01035.x</t>
         </is>
       </c>
       <c r="N130" s="4" t="n"/>
@@ -9007,18 +9033,18 @@
       </c>
       <c r="C131" s="35" t="inlineStr">
         <is>
-          <t>Levoye et al., 2015</t>
+          <t>Gulappa et al., 2011</t>
         </is>
       </c>
       <c r="D131" s="4" t="n"/>
-      <c r="E131" s="34" t="inlineStr">
-        <is>
-          <t>CXCR7</t>
+      <c r="E131" s="82" t="inlineStr">
+        <is>
+          <t>LHR</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Fluorescence Microscopy</t>
+          <t>Western Blot</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -9028,19 +9054,21 @@
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>0.0606 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>SR26</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3389/fendo.2015.00167</t>
-        </is>
-      </c>
+          <t>0.0033 ± 0.0003</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>SR15</t>
+        </is>
+      </c>
+      <c r="M131" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1007/s00018-010-0594-1</t>
+        </is>
+      </c>
+      <c r="N131" s="4" t="n"/>
+      <c r="O131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="51" t="inlineStr">
@@ -9053,15 +9081,15 @@
           <t>OXTR recycling rate (back to surface)</t>
         </is>
       </c>
-      <c r="C132" s="69" t="inlineStr">
-        <is>
-          <t>Bulseco, Thesis 1996</t>
+      <c r="C132" s="35" t="inlineStr">
+        <is>
+          <t>Ghosh, et al., 1994</t>
         </is>
       </c>
       <c r="D132" s="4" t="n"/>
-      <c r="E132" s="83" t="inlineStr">
-        <is>
-          <t>M2R</t>
+      <c r="E132" s="34" t="inlineStr">
+        <is>
+          <t>TR</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -9076,19 +9104,21 @@
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>0.013 ± 0.002</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>SR5</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
-        </is>
-      </c>
+          <t>0.09902 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>SR14</t>
+        </is>
+      </c>
+      <c r="M132" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1242/jcs.107.8.2177</t>
+        </is>
+      </c>
+      <c r="N132" s="4" t="n"/>
+      <c r="O132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="51" t="inlineStr">
@@ -9101,40 +9131,40 @@
           <t>OXTR recycling rate (back to surface)</t>
         </is>
       </c>
-      <c r="C133" s="70" t="inlineStr">
-        <is>
-          <t>Thibonnier et al., 2001</t>
-        </is>
-      </c>
-      <c r="D133" s="84" t="n"/>
-      <c r="E133" s="78" t="inlineStr">
-        <is>
-          <t>V1R</t>
-        </is>
-      </c>
-      <c r="F133" s="65" t="inlineStr">
-        <is>
-          <t>Radioligand binding assays</t>
-        </is>
-      </c>
-      <c r="G133" s="64" t="inlineStr">
-        <is>
-          <t>CHO cells</t>
-        </is>
-      </c>
-      <c r="H133" s="28" t="inlineStr">
-        <is>
-          <t>0.036 ± 0.00</t>
+      <c r="C133" s="35" t="inlineStr">
+        <is>
+          <t>Levoye et al., 2015</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="34" t="inlineStr">
+        <is>
+          <t>CXCR7</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>Fluorescence Microscopy</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>0.0606 ± 0.00</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>SR49</t>
+          <t>SR26</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
+          <t>https://doi.org/10.3389/fendo.2015.00167</t>
         </is>
       </c>
     </row>
@@ -9149,148 +9179,148 @@
           <t>OXTR recycling rate (back to surface)</t>
         </is>
       </c>
-      <c r="C134" s="35" t="inlineStr">
+      <c r="C134" s="69" t="inlineStr">
+        <is>
+          <t>Bulseco, Thesis 1996</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="83" t="inlineStr">
+        <is>
+          <t>M2R</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Radiolabelling</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>0.013 ± 0.002</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>SR5</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="51" t="inlineStr">
+        <is>
+          <t>Krec</t>
+        </is>
+      </c>
+      <c r="B135" s="53" t="inlineStr">
+        <is>
+          <t>OXTR recycling rate (back to surface)</t>
+        </is>
+      </c>
+      <c r="C135" s="70" t="inlineStr">
+        <is>
+          <t>Thibonnier et al., 2001</t>
+        </is>
+      </c>
+      <c r="D135" s="84" t="n"/>
+      <c r="E135" s="78" t="inlineStr">
+        <is>
+          <t>V1R</t>
+        </is>
+      </c>
+      <c r="F135" s="65" t="inlineStr">
+        <is>
+          <t>Radioligand binding assays</t>
+        </is>
+      </c>
+      <c r="G135" s="64" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
+        </is>
+      </c>
+      <c r="H135" s="28" t="inlineStr">
+        <is>
+          <t>0.036 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>SR49</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1152/ajpendo.2001.281.1.E81</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1">
+      <c r="A136" s="51" t="inlineStr">
+        <is>
+          <t>Krec</t>
+        </is>
+      </c>
+      <c r="B136" s="53" t="inlineStr">
+        <is>
+          <t>OXTR recycling rate (back to surface)</t>
+        </is>
+      </c>
+      <c r="C136" s="35" t="inlineStr">
         <is>
           <t>Wiley, et al., 1991</t>
         </is>
       </c>
-      <c r="D134" s="4" t="n"/>
-      <c r="E134" s="34" t="inlineStr">
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="34" t="inlineStr">
         <is>
           <t>TR</t>
         </is>
       </c>
-      <c r="F134" s="4" t="inlineStr">
+      <c r="F136" s="4" t="inlineStr">
         <is>
           <t>Radiolabelling</t>
         </is>
       </c>
-      <c r="G134" s="4" t="inlineStr">
+      <c r="G136" s="4" t="inlineStr">
         <is>
           <t>B82 fribroblasts</t>
         </is>
       </c>
-      <c r="H134" s="8" t="inlineStr">
+      <c r="H136" s="8" t="inlineStr">
         <is>
           <t>0.13 ± 0.02</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t>SR54</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t>https://doi.org/10.1016/s0021-9258(18)99131-3</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="1" t="n"/>
-      <c r="B135" s="1" t="n"/>
-      <c r="C135" s="68" t="n"/>
-      <c r="D135" s="4" t="n"/>
-      <c r="E135" s="44" t="n"/>
-      <c r="F135" s="1" t="n"/>
-      <c r="G135" s="1" t="n"/>
-      <c r="H135" s="9" t="n"/>
-    </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="57" t="inlineStr">
-        <is>
-          <t>Kins</t>
-        </is>
-      </c>
-      <c r="B136" s="66" t="inlineStr">
-        <is>
-          <t>Export rate constant of receptor from Golgi/ER/Nucleus Complex to plasma membrane</t>
-        </is>
-      </c>
-      <c r="C136" s="29" t="inlineStr">
-        <is>
-          <t>Zhang, et al., 2016</t>
-        </is>
-      </c>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="30" t="inlineStr">
-        <is>
-          <t>α2AR</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>Ligand binding</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H136" s="11" t="inlineStr">
-        <is>
-          <t>0.0011 ± 0.00</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>SR57</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1128/mcb.00009-16</t>
-        </is>
-      </c>
-    </row>
     <row r="137" ht="60" customHeight="1">
-      <c r="A137" s="57" t="inlineStr">
-        <is>
-          <t>Kins</t>
-        </is>
-      </c>
-      <c r="B137" s="66" t="inlineStr">
-        <is>
-          <t>Export rate constant of receptor from Golgi/ER/Nucleus Complex to plasma membrane</t>
-        </is>
-      </c>
-      <c r="C137" s="35" t="inlineStr">
-        <is>
-          <t>Patterson et al., 2008</t>
-        </is>
-      </c>
+      <c r="A137" s="1" t="n"/>
+      <c r="B137" s="1" t="n"/>
+      <c r="C137" s="68" t="n"/>
       <c r="D137" s="4" t="n"/>
-      <c r="E137" s="34" t="inlineStr">
-        <is>
-          <t>VSVG-GFP</t>
-        </is>
-      </c>
-      <c r="F137" s="4" t="inlineStr">
-        <is>
-          <t>Fluorescence Microscopy</t>
-        </is>
-      </c>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>COS7 cells</t>
-        </is>
-      </c>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>0.0545 ± 0.0155</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>SR41</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.cell.2008.04.044</t>
-        </is>
-      </c>
+      <c r="E137" s="44" t="n"/>
+      <c r="F137" s="1" t="n"/>
+      <c r="G137" s="1" t="n"/>
+      <c r="H137" s="9" t="n"/>
     </row>
     <row r="138" ht="60" customHeight="1">
       <c r="A138" s="57" t="inlineStr">
@@ -9303,40 +9333,40 @@
           <t>Export rate constant of receptor from Golgi/ER/Nucleus Complex to plasma membrane</t>
         </is>
       </c>
-      <c r="C138" s="35" t="inlineStr">
-        <is>
-          <t>Bulseco, Thesis 1996</t>
+      <c r="C138" s="29" t="inlineStr">
+        <is>
+          <t>Zhang, et al., 2016</t>
         </is>
       </c>
       <c r="D138" s="4" t="n"/>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>M2R</t>
-        </is>
-      </c>
-      <c r="F138" s="4" t="inlineStr">
-        <is>
-          <t>Radiolabelling</t>
-        </is>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>CHO cells</t>
-        </is>
-      </c>
-      <c r="H138" s="8" t="inlineStr">
-        <is>
-          <t>0.035265 ± 0.033735</t>
+      <c r="E138" s="30" t="inlineStr">
+        <is>
+          <t>α2AR</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>Ligand binding</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
+        </is>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>0.0011 ± 0.00</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>SR5</t>
+          <t>SR57</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+          <t>https://doi.org/10.1128/mcb.00009-16</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9383,7 @@
       </c>
       <c r="C139" s="35" t="inlineStr">
         <is>
-          <t>Hirschberg, K et al. 1998</t>
+          <t>Patterson et al., 2008</t>
         </is>
       </c>
       <c r="D139" s="4" t="n"/>
@@ -9374,44 +9404,82 @@
       </c>
       <c r="H139" s="8" t="inlineStr">
         <is>
-          <t>0.0303 ± 0.0026</t>
+          <t>0.0545 ± 0.0155</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>SR19</t>
+          <t>SR41</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1083/jcb.143.6.1485</t>
+          <t>https://doi.org/10.1016/j.cell.2008.04.044</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n"/>
-      <c r="B140" s="1" t="n"/>
-      <c r="C140" s="68" t="n"/>
+      <c r="A140" s="57" t="inlineStr">
+        <is>
+          <t>Kins</t>
+        </is>
+      </c>
+      <c r="B140" s="66" t="inlineStr">
+        <is>
+          <t>Export rate constant of receptor from Golgi/ER/Nucleus Complex to plasma membrane</t>
+        </is>
+      </c>
+      <c r="C140" s="35" t="inlineStr">
+        <is>
+          <t>Bulseco, Thesis 1996</t>
+        </is>
+      </c>
       <c r="D140" s="4" t="n"/>
-      <c r="E140" s="44" t="n"/>
-      <c r="F140" s="1" t="n"/>
-      <c r="G140" s="1" t="n"/>
-      <c r="H140" s="9" t="n"/>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>M2R</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Radiolabelling</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>CHO cells</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>0.035265 ± 0.033735</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>SR5</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/s0026-895x(25)08679-1</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="52" t="inlineStr">
-        <is>
-          <t>Krgt</t>
-        </is>
-      </c>
-      <c r="B141" s="67" t="inlineStr">
-        <is>
-          <t>Retrograde transport to Golgi</t>
+      <c r="A141" s="57" t="inlineStr">
+        <is>
+          <t>Kins</t>
+        </is>
+      </c>
+      <c r="B141" s="66" t="inlineStr">
+        <is>
+          <t>Export rate constant of receptor from Golgi/ER/Nucleus Complex to plasma membrane</t>
         </is>
       </c>
       <c r="C141" s="35" t="inlineStr">
         <is>
-          <t>Starr, et al., 2007</t>
+          <t>Hirschberg, K et al. 1998</t>
         </is>
       </c>
       <c r="D141" s="4" t="n"/>
@@ -9422,77 +9490,39 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Fluorescence microscopy</t>
+          <t>Fluorescence Microscopy</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Hela Cells</t>
+          <t>COS7 cells</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>0.0375 ± 0.0175</t>
+          <t>0.0303 ± 0.0026</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>SR47</t>
+          <t>SR19</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1111/j.1600-0854.2007.00607.x</t>
+          <t>https://doi.org/10.1083/jcb.143.6.1485</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="52" t="inlineStr">
-        <is>
-          <t>Krgt</t>
-        </is>
-      </c>
-      <c r="B142" s="67" t="inlineStr">
-        <is>
-          <t>Retrograde transport to Golgi</t>
-        </is>
-      </c>
-      <c r="C142" s="35" t="inlineStr">
-        <is>
-          <t>Ure, et al., 1997</t>
-        </is>
-      </c>
+      <c r="A142" s="1" t="n"/>
+      <c r="B142" s="1" t="n"/>
+      <c r="C142" s="68" t="n"/>
       <c r="D142" s="4" t="n"/>
-      <c r="E142" s="5" t="inlineStr">
-        <is>
-          <t>INGF</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Radiolabelling</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
-        <is>
-          <t>Rat Sympathetic Neurons</t>
-        </is>
-      </c>
-      <c r="H142" s="8" t="inlineStr">
-        <is>
-          <t>0.00233 ± 7.0E-5</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>SR52</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1523/jneurosci.17-04-01282.1997</t>
-        </is>
-      </c>
+      <c r="E142" s="44" t="n"/>
+      <c r="F142" s="1" t="n"/>
+      <c r="G142" s="1" t="n"/>
+      <c r="H142" s="9" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="52" t="inlineStr">
@@ -9507,7 +9537,7 @@
       </c>
       <c r="C143" s="35" t="inlineStr">
         <is>
-          <t>Hirschberg, K et al. 1998</t>
+          <t>Starr, et al., 2007</t>
         </is>
       </c>
       <c r="D143" s="4" t="n"/>
@@ -9518,27 +9548,27 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Fluorescence Microscopy</t>
+          <t>Fluorescence microscopy</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>COS7 cells</t>
+          <t>Hela Cells</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>0.0284 ± 0.002</t>
+          <t>0.0375 ± 0.0175</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>SR19</t>
+          <t>SR47</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1083/jcb.143.6.1485</t>
+          <t>https://doi.org/10.1111/j.1600-0854.2007.00607.x</t>
         </is>
       </c>
     </row>
@@ -9553,40 +9583,40 @@
           <t>Retrograde transport to Golgi</t>
         </is>
       </c>
-      <c r="C144" s="149" t="inlineStr">
-        <is>
-          <t>Buser et al., 2022</t>
+      <c r="C144" s="35" t="inlineStr">
+        <is>
+          <t>Ure, et al., 1997</t>
         </is>
       </c>
       <c r="D144" s="4" t="n"/>
-      <c r="E144" s="110" t="inlineStr">
-        <is>
-          <t>EGFP-CDMPR</t>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>INGF</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Fluorescence Microscopy</t>
+          <t>Radiolabelling</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>Hela Cells</t>
+          <t>Rat Sympathetic Neurons</t>
         </is>
       </c>
       <c r="H144" s="8" t="inlineStr">
         <is>
-          <t>0.94796 ± 0.00</t>
+          <t>0.00233 ± 7.0E-5</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>SR6</t>
+          <t>SR52</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>https://doi.org/10.26508/lsa.202101269</t>
+          <t>https://doi.org/10.1523/jneurosci.17-04-01282.1997</t>
         </is>
       </c>
     </row>
@@ -9601,15 +9631,15 @@
           <t>Retrograde transport to Golgi</t>
         </is>
       </c>
-      <c r="C145" s="149" t="inlineStr">
-        <is>
-          <t>Buser et al., 2022</t>
+      <c r="C145" s="35" t="inlineStr">
+        <is>
+          <t>Hirschberg, K et al. 1998</t>
         </is>
       </c>
       <c r="D145" s="4" t="n"/>
-      <c r="E145" s="110" t="inlineStr">
-        <is>
-          <t>EGFP-CDMPR</t>
+      <c r="E145" s="34" t="inlineStr">
+        <is>
+          <t>VSVG-GFP</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -9619,22 +9649,22 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>Hela Cells</t>
+          <t>COS7 cells</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>0.043513 ± 0.00</t>
+          <t>0.0284 ± 0.002</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>SR6</t>
+          <t>SR19</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>https://doi.org/10.26508/lsa.202101269</t>
+          <t>https://doi.org/10.1083/jcb.143.6.1485</t>
         </is>
       </c>
     </row>
@@ -9672,7 +9702,7 @@
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>0.1815007 ± 0.00</t>
+          <t>0.94796 ± 0.00</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -9720,125 +9750,125 @@
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
+          <t>0.043513 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>SR6</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.26508/lsa.202101269</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="52" t="inlineStr">
+        <is>
+          <t>Krgt</t>
+        </is>
+      </c>
+      <c r="B148" s="67" t="inlineStr">
+        <is>
+          <t>Retrograde transport to Golgi</t>
+        </is>
+      </c>
+      <c r="C148" s="149" t="inlineStr">
+        <is>
+          <t>Buser et al., 2022</t>
+        </is>
+      </c>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="110" t="inlineStr">
+        <is>
+          <t>EGFP-CDMPR</t>
+        </is>
+      </c>
+      <c r="F148" s="4" t="inlineStr">
+        <is>
+          <t>Fluorescence Microscopy</t>
+        </is>
+      </c>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>Hela Cells</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>0.1815007 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>SR6</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.26508/lsa.202101269</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="52" t="inlineStr">
+        <is>
+          <t>Krgt</t>
+        </is>
+      </c>
+      <c r="B149" s="67" t="inlineStr">
+        <is>
+          <t>Retrograde transport to Golgi</t>
+        </is>
+      </c>
+      <c r="C149" s="149" t="inlineStr">
+        <is>
+          <t>Buser et al., 2022</t>
+        </is>
+      </c>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="110" t="inlineStr">
+        <is>
+          <t>EGFP-CDMPR</t>
+        </is>
+      </c>
+      <c r="F149" s="4" t="inlineStr">
+        <is>
+          <t>Fluorescence Microscopy</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>Hela Cells</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
           <t>0.473003 ± 0.00</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t>SR6</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>https://doi.org/10.26508/lsa.202101269</t>
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="1" t="n"/>
-      <c r="B148" s="1" t="n"/>
-      <c r="C148" s="68" t="n"/>
-      <c r="D148" s="4" t="n"/>
-      <c r="E148" s="44" t="n"/>
-      <c r="F148" s="1" t="n"/>
-      <c r="G148" s="1" t="n"/>
-      <c r="H148" s="9" t="n"/>
-    </row>
-    <row r="149" ht="60" customHeight="1">
-      <c r="A149" s="57" t="inlineStr">
-        <is>
-          <t>Kdeg</t>
-        </is>
-      </c>
-      <c r="B149" s="66" t="inlineStr">
-        <is>
-          <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
-        </is>
-      </c>
-      <c r="C149" s="50" t="inlineStr">
-        <is>
-          <t>Lee, et al., 2021</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="n"/>
-      <c r="E149" s="172" t="inlineStr">
-        <is>
-          <t>α1AR</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>SNAP-CHX-Chase Assays</t>
-        </is>
-      </c>
-      <c r="G149" s="3" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H149" s="11" t="inlineStr">
-        <is>
-          <t>0.008708 ± 0.001488</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>SR25</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1177/2472555220979793</t>
-        </is>
-      </c>
-    </row>
     <row r="150" ht="60" customHeight="1">
-      <c r="A150" s="57" t="inlineStr">
-        <is>
-          <t>Kdeg</t>
-        </is>
-      </c>
-      <c r="B150" s="66" t="inlineStr">
-        <is>
-          <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
-        </is>
-      </c>
-      <c r="C150" s="107" t="inlineStr">
-        <is>
-          <t>Lee, et al., 2021</t>
-        </is>
-      </c>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="173" t="inlineStr">
-        <is>
-          <t>α2AR</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>SNAP-CHX-Chase Assays</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>HEK293 Cells</t>
-        </is>
-      </c>
-      <c r="H150" s="8" t="inlineStr">
-        <is>
-          <t>0.005700 ± 0.0006110</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>SR25</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1177/2472555220979793</t>
-        </is>
-      </c>
+      <c r="A150" s="1" t="n"/>
+      <c r="B150" s="1" t="n"/>
+      <c r="C150" s="68" t="n"/>
+      <c r="D150" s="4" t="n"/>
+      <c r="E150" s="44" t="n"/>
+      <c r="F150" s="1" t="n"/>
+      <c r="G150" s="1" t="n"/>
+      <c r="H150" s="9" t="n"/>
     </row>
     <row r="151" ht="60" customHeight="1">
       <c r="A151" s="57" t="inlineStr">
@@ -9851,30 +9881,30 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C151" s="107" t="inlineStr">
+      <c r="C151" s="50" t="inlineStr">
         <is>
           <t>Lee, et al., 2021</t>
         </is>
       </c>
-      <c r="D151" s="7" t="n"/>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>βXAR</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
+      <c r="D151" s="4" t="n"/>
+      <c r="E151" s="172" t="inlineStr">
+        <is>
+          <t>α1AR</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>SNAP-CHX-Chase Assays</t>
         </is>
       </c>
-      <c r="G151" s="7" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>HEK293 Cells</t>
         </is>
       </c>
-      <c r="H151" s="8" t="inlineStr">
-        <is>
-          <t>0.005965 ± 0.0009856</t>
+      <c r="H151" s="11" t="inlineStr">
+        <is>
+          <t>0.008708 ± 0.001488</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -9907,7 +9937,7 @@
       <c r="D152" s="7" t="n"/>
       <c r="E152" s="173" t="inlineStr">
         <is>
-          <t>5-HTX</t>
+          <t>α2AR</t>
         </is>
       </c>
       <c r="F152" s="7" t="inlineStr">
@@ -9922,7 +9952,7 @@
       </c>
       <c r="H152" s="8" t="inlineStr">
         <is>
-          <t>0.004507 ± 0.0006560</t>
+          <t>0.005700 ± 0.0006110</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -9953,9 +9983,9 @@
         </is>
       </c>
       <c r="D153" s="7" t="n"/>
-      <c r="E153" s="173" t="inlineStr">
-        <is>
-          <t>SSTR</t>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>βXAR</t>
         </is>
       </c>
       <c r="F153" s="7" t="inlineStr">
@@ -9970,7 +10000,7 @@
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>0.007453 ± 0.001447</t>
+          <t>0.005965 ± 0.0009856</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -10003,7 +10033,7 @@
       <c r="D154" s="7" t="n"/>
       <c r="E154" s="173" t="inlineStr">
         <is>
-          <t>CXCR</t>
+          <t>5-HTX</t>
         </is>
       </c>
       <c r="F154" s="7" t="inlineStr">
@@ -10018,7 +10048,7 @@
       </c>
       <c r="H154" s="8" t="inlineStr">
         <is>
-          <t>0.006515 ± 0.001183</t>
+          <t>0.004507 ± 0.0006560</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -10043,40 +10073,40 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C155" s="35" t="inlineStr">
-        <is>
-          <t>S. L. Shyng &amp; M. M. Salpeter 1989</t>
-        </is>
-      </c>
-      <c r="D155" s="4" t="n"/>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>AChR</t>
-        </is>
-      </c>
-      <c r="F155" s="4" t="inlineStr">
-        <is>
-          <t>TEM autoradiography</t>
-        </is>
-      </c>
-      <c r="G155" s="4" t="inlineStr">
-        <is>
-          <t>adult female white mice</t>
+      <c r="C155" s="107" t="inlineStr">
+        <is>
+          <t>Lee, et al., 2021</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="n"/>
+      <c r="E155" s="173" t="inlineStr">
+        <is>
+          <t>SSTR</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>SNAP-CHX-Chase Assays</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>0.00042675 ± 0.00007635</t>
+          <t>0.007453 ± 0.001447</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>SR45</t>
+          <t>SR25</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1083/jcb.108.2.647</t>
+          <t>https://doi.org/10.1177/2472555220979793</t>
         </is>
       </c>
     </row>
@@ -10091,40 +10121,40 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C156" s="76" t="inlineStr">
-        <is>
-          <t>Merlie et al., 1979</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="n"/>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>AChR</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Radiolabelling</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>Female Lewis rat</t>
+      <c r="C156" s="107" t="inlineStr">
+        <is>
+          <t>Lee, et al., 2021</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="n"/>
+      <c r="E156" s="173" t="inlineStr">
+        <is>
+          <t>CXCR</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>SNAP-CHX-Chase Assays</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
         </is>
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>0.000680 ± 0.00</t>
+          <t>0.006515 ± 0.001183</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>SR34</t>
+          <t>SR25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/s0021-9258(18)50365-3</t>
+          <t>https://doi.org/10.1177/2472555220979793</t>
         </is>
       </c>
     </row>
@@ -10139,40 +10169,40 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C157" s="71" t="inlineStr">
-        <is>
-          <t>Vicentic et al., 2000</t>
+      <c r="C157" s="35" t="inlineStr">
+        <is>
+          <t>S. L. Shyng &amp; M. M. Salpeter 1989</t>
         </is>
       </c>
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>5-HT1A</t>
+          <t>AChR</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Radiolabelling</t>
+          <t>TEM autoradiography</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
         <is>
-          <t>Pregnant Sprague–Dawley rat</t>
+          <t>adult female white mice</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>0.000105 ± 0.00</t>
+          <t>0.00042675 ± 0.00007635</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>SR53</t>
+          <t>SR45</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0006-8993(00)02668-8</t>
+          <t>https://doi.org/10.1083/jcb.108.2.647</t>
         </is>
       </c>
     </row>
@@ -10187,42 +10217,40 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C158" s="170" t="inlineStr">
-        <is>
-          <t>Vicentic et al., 2000</t>
-        </is>
-      </c>
-      <c r="D158" s="171" t="n"/>
+      <c r="C158" s="76" t="inlineStr">
+        <is>
+          <t>Merlie et al., 1979</t>
+        </is>
+      </c>
+      <c r="D158" s="4" t="n"/>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>5-HT2A</t>
-        </is>
-      </c>
-      <c r="F158" s="5" t="inlineStr">
+          <t>AChR</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>Radiolabelling</t>
         </is>
       </c>
-      <c r="G158" s="5" t="inlineStr">
-        <is>
-          <t>Pregnant Sprague–Dawley rat</t>
-        </is>
-      </c>
-      <c r="H158" s="109" t="inlineStr">
-        <is>
-          <t>0.000102 ± 0.00</t>
-        </is>
-      </c>
-      <c r="I158" s="141" t="n"/>
-      <c r="J158" s="141" t="n"/>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>Female Lewis rat</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>0.000680 ± 0.00</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>SR53</t>
+          <t>SR34</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/S0006-8993(00)02668-8</t>
+          <t>https://doi.org/10.1016/s0021-9258(18)50365-3</t>
         </is>
       </c>
     </row>
@@ -10237,15 +10265,15 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C159" s="35" t="inlineStr">
-        <is>
-          <t>Liang &amp; Fishman, 2004</t>
+      <c r="C159" s="71" t="inlineStr">
+        <is>
+          <t>Vicentic et al., 2000</t>
         </is>
       </c>
       <c r="D159" s="4" t="n"/>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>β2AR</t>
+      <c r="E159" s="5" t="inlineStr">
+        <is>
+          <t>5-HT1A</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -10255,22 +10283,22 @@
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>HEK293 Cells</t>
+          <t>Pregnant Sprague–Dawley rat</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>0.00177 ± 0.00</t>
+          <t>0.000105 ± 0.00</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>SR28</t>
+          <t>SR53</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1074/jbc.M406501200</t>
+          <t>https://doi.org/10.1016/S0006-8993(00)02668-8</t>
         </is>
       </c>
     </row>
@@ -10285,40 +10313,42 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C160" s="76" t="inlineStr">
-        <is>
-          <t>Fambrough et al., 1979</t>
-        </is>
-      </c>
-      <c r="D160" s="4" t="n"/>
+      <c r="C160" s="170" t="inlineStr">
+        <is>
+          <t>Vicentic et al., 2000</t>
+        </is>
+      </c>
+      <c r="D160" s="171" t="n"/>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>AChR</t>
-        </is>
-      </c>
-      <c r="F160" s="4" t="inlineStr">
+          <t>5-HT2A</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
         <is>
           <t>Radiolabelling</t>
         </is>
       </c>
-      <c r="G160" s="4" t="inlineStr">
-        <is>
-          <t>Chicken leg skeletal muscle</t>
-        </is>
-      </c>
-      <c r="H160" s="8" t="inlineStr">
-        <is>
-          <t>0.00064 ± 0.00</t>
-        </is>
-      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>Pregnant Sprague–Dawley rat</t>
+        </is>
+      </c>
+      <c r="H160" s="109" t="inlineStr">
+        <is>
+          <t>0.000102 ± 0.00</t>
+        </is>
+      </c>
+      <c r="I160" s="141" t="n"/>
+      <c r="J160" s="141" t="n"/>
       <c r="L160" t="inlineStr">
         <is>
-          <t>SR11</t>
+          <t>SR53</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1152/physrev.1979.59.1.165</t>
+          <t>https://doi.org/10.1016/S0006-8993(00)02668-8</t>
         </is>
       </c>
     </row>
@@ -10333,38 +10363,134 @@
           <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
         </is>
       </c>
-      <c r="C161" s="76" t="inlineStr">
+      <c r="C161" s="35" t="inlineStr">
+        <is>
+          <t>Liang &amp; Fishman, 2004</t>
+        </is>
+      </c>
+      <c r="D161" s="4" t="n"/>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>β2AR</t>
+        </is>
+      </c>
+      <c r="F161" s="4" t="inlineStr">
+        <is>
+          <t>Radiolabelling</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>HEK293 Cells</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
+          <t>0.00177 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>SR28</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1074/jbc.M406501200</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="57" t="inlineStr">
+        <is>
+          <t>Kdeg</t>
+        </is>
+      </c>
+      <c r="B162" s="66" t="inlineStr">
+        <is>
+          <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
+        </is>
+      </c>
+      <c r="C162" s="76" t="inlineStr">
+        <is>
+          <t>Fambrough et al., 1979</t>
+        </is>
+      </c>
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>AChR</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
+        <is>
+          <t>Radiolabelling</t>
+        </is>
+      </c>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>Chicken leg skeletal muscle</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>0.00064 ± 0.00</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>SR11</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1152/physrev.1979.59.1.165</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="57" t="inlineStr">
+        <is>
+          <t>Kdeg</t>
+        </is>
+      </c>
+      <c r="B163" s="66" t="inlineStr">
+        <is>
+          <t>Total receptor degradation rate (or based on the schematic, it means receptor trafficking to lysosome?)</t>
+        </is>
+      </c>
+      <c r="C163" s="76" t="inlineStr">
         <is>
           <t>Hirschberg, K et al. 1998</t>
         </is>
       </c>
-      <c r="D161" s="4" t="n"/>
-      <c r="E161" s="34" t="inlineStr">
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="34" t="inlineStr">
         <is>
           <t>VSVG-GFP</t>
         </is>
       </c>
-      <c r="F161" s="4" t="inlineStr">
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>Fluorescence Microscopy</t>
         </is>
       </c>
-      <c r="G161" s="4" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr">
         <is>
           <t>COS-7 Cells</t>
         </is>
       </c>
-      <c r="H161" s="8" t="inlineStr">
+      <c r="H163" s="8" t="inlineStr">
         <is>
           <t>0.00255 ± 0.00034</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t>SR19</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t>https://doi.org/10.1083/jcb.143.6.1485</t>
         </is>
